--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carreño\Documents\Nico\Git\Brumario\backend\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFEDE2F-B9AE-421F-B996-882D7E57D088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7050"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t>Nombre</t>
   </si>
@@ -516,12 +517,15 @@
   </si>
   <si>
     <t>Yafar, Yamil</t>
+  </si>
+  <si>
+    <t>2Giménez, Ariel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -614,7 +618,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -891,834 +895,834 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B166"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B76" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B83" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B85" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B87" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B90" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B91" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B92" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B95" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B96" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B97" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B98" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B99" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B100" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B101" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B102" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B103" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B104" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B105" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B106" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B107" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B108" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B109" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B110" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B111" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B112" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B113" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B114" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B115" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B118" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B119" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B124" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B125" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B126" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B127" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B128" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B129" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B130" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B131" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B132" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B133" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B134" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B135" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B136" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B137" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B138" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B139" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B140" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B141" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B143" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B144" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B146" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B147" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B148" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B150" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B151" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B152" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B153" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B154" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B156" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B157" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B158" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B159" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B160" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B161" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B162" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B163" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B164" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B165" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B166" s="3" t="s">
         <v>163</v>
       </c>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\GitHub\Brumario\backend\src\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\Nico\brumario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFEDE2F-B9AE-421F-B996-882D7E57D088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54221394-C181-4ABF-A221-472230963769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>Nombre</t>
   </si>
@@ -517,6 +517,15 @@
   </si>
   <si>
     <t>Yafar, Yamil</t>
+  </si>
+  <si>
+    <t>Debut</t>
+  </si>
+  <si>
+    <t>Debut Oficial</t>
+  </si>
+  <si>
+    <t>Dorsal</t>
   </si>
   <si>
     <t>2Giménez, Ariel</t>
@@ -526,7 +535,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,15 +558,46 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -604,7 +648,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -613,6 +657,54 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -896,838 +988,1625 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B166"/>
+  <dimension ref="B2:E166"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.26953125" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C11" s="5">
+        <v>45472</v>
+      </c>
+      <c r="D11" s="5">
+        <v>45472</v>
+      </c>
+      <c r="E11" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C13" s="5">
+        <v>45361</v>
+      </c>
+      <c r="D13" s="5">
+        <v>45396</v>
+      </c>
+      <c r="E13" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C14" s="5">
+        <v>45164</v>
+      </c>
+      <c r="D14" s="5">
+        <v>45200</v>
+      </c>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C17" s="6">
+        <v>44422</v>
+      </c>
+      <c r="D17" s="6">
+        <v>44436</v>
+      </c>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C18" s="5">
+        <v>44793</v>
+      </c>
+      <c r="D18" s="5">
+        <v>44807</v>
+      </c>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C19" s="7">
+        <v>45220</v>
+      </c>
+      <c r="D19" s="7">
+        <v>45220</v>
+      </c>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C23" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D23" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C26" s="9">
+        <v>44739</v>
+      </c>
+      <c r="D26" s="9">
+        <v>44746</v>
+      </c>
+      <c r="E26" s="10">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C27" s="8">
+        <v>45164</v>
+      </c>
+      <c r="D27" s="11">
+        <v>45220</v>
+      </c>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C31" s="4"/>
+      <c r="D31" s="12">
+        <v>42161</v>
+      </c>
+      <c r="E31" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C34" s="8">
+        <v>44758</v>
+      </c>
+      <c r="D34" s="8">
+        <v>44758</v>
+      </c>
+      <c r="E34" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C44" s="8">
+        <v>45395</v>
+      </c>
+      <c r="D44" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E44" s="14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C46" s="12">
+        <v>43652</v>
+      </c>
+      <c r="D46" s="12">
+        <v>43722</v>
+      </c>
+      <c r="E46" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C48" s="15">
+        <v>42294</v>
+      </c>
+      <c r="D48" s="12">
+        <v>42294</v>
+      </c>
+      <c r="E48" s="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C51" s="8">
+        <v>45395</v>
+      </c>
+      <c r="D51" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E51" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C52" s="4"/>
+      <c r="D52" s="12">
+        <v>42161</v>
+      </c>
+      <c r="E52" s="13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C53" s="9">
+        <v>44739</v>
+      </c>
+      <c r="D53" s="9">
+        <v>44746</v>
+      </c>
+      <c r="E53" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C54" s="8">
+        <v>43708</v>
+      </c>
+      <c r="D54" s="8">
+        <v>44716</v>
+      </c>
+      <c r="E54" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C55" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D55" s="8">
+        <v>45038</v>
+      </c>
+      <c r="E55" s="13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C56" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D56" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E56" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C57" s="8">
+        <v>45374</v>
+      </c>
+      <c r="D57" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E57" s="4"/>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C59" s="9">
+        <v>44226</v>
+      </c>
+      <c r="D59" s="9">
+        <v>44436</v>
+      </c>
+      <c r="E59" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C61" s="4"/>
+      <c r="D61" s="12">
+        <v>42161</v>
+      </c>
+      <c r="E61" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C66" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D66" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E66" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C70" s="12">
+        <v>43890</v>
+      </c>
+      <c r="D70" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E70" s="13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C71" s="8">
+        <v>45361</v>
+      </c>
+      <c r="D71" s="8">
+        <v>45403</v>
+      </c>
+      <c r="E71" s="4"/>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C72" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D72" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B76" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B76" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C80" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D80" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E80" s="14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C81" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D81" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E81" s="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B83" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B87" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B90" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B91" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C91" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D91" s="16">
+        <v>44723</v>
+      </c>
+      <c r="E91" s="4"/>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B92" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B95" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B96" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B105" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C105" s="16">
+        <v>44961</v>
+      </c>
+      <c r="D105" s="16">
+        <v>45038</v>
+      </c>
+      <c r="E105" s="4"/>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B106" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C106" s="8">
+        <v>45403</v>
+      </c>
+      <c r="D106" s="8">
+        <v>45403</v>
+      </c>
+      <c r="E106" s="14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B107" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C107" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D107" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E107" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B108" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B109" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C109" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D109" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E109" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B110" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B111" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B112" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B113" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B114" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B115" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C115" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D115" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E115" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B118" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C118" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D118" s="8">
+        <v>45556</v>
+      </c>
+      <c r="E118" s="4"/>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B119" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C119" s="8">
+        <v>45273</v>
+      </c>
+      <c r="D119" s="8">
+        <v>45273</v>
+      </c>
+      <c r="E119" s="4"/>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B124" s="1" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B125" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C125" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D125" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E125" s="13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B126" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B127" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="4"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B128" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B129" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C129" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D129" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E129" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B130" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B131" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C131" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D131" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E131" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B132" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B133" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C133" s="15">
+        <v>39760</v>
+      </c>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B134" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B135" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C135" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D135" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E135" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B136" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C136" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D136" s="8">
+        <v>44811</v>
+      </c>
+      <c r="E136" s="13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B137" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B138" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C138" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D138" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E138" s="13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B139" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B140" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B141" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B143" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B144" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B146" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B147" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C147" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D147" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E147" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B148" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B150" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B151" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B152" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B153" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B154" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C154" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D154" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E154" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B156" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B157" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B158" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C158" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D158" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E158" s="13">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B159" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B160" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B161" s="1" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B162" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B163" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B164" s="1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C164" s="15">
+        <v>42350</v>
+      </c>
+      <c r="D164" s="12">
+        <v>42532</v>
+      </c>
+      <c r="E164" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B165" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B166" s="3" t="s">
         <v>163</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\Nico\brumario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54221394-C181-4ABF-A221-472230963769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1AA86B-291A-4771-98BF-891D5C23A682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>Nombre</t>
   </si>
@@ -529,6 +540,18 @@
   </si>
   <si>
     <t>2Giménez, Ariel</t>
+  </si>
+  <si>
+    <t>Giorgio, Diego</t>
+  </si>
+  <si>
+    <t>Lacava, Valentino</t>
+  </si>
+  <si>
+    <t>Nuñez, Lautaro</t>
+  </si>
+  <si>
+    <t>Zenobi, Laureano</t>
   </si>
 </sst>
 </file>
@@ -539,7 +562,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +596,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -600,7 +628,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -643,12 +671,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -659,53 +705,68 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -988,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E166"/>
+  <dimension ref="B2:E170"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.26953125" customWidth="1"/>
@@ -1757,16 +1818,20 @@
       <c r="E76" s="4"/>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B77" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
+      <c r="B77" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="20">
+        <v>45913</v>
+      </c>
+      <c r="D77" s="20">
+        <v>45913</v>
+      </c>
       <c r="E77" s="4"/>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -1774,7 +1839,7 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -1782,43 +1847,43 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D80" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E80" s="14">
-        <v>31</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81" s="12">
-        <v>41832</v>
-      </c>
-      <c r="D81" s="12">
-        <v>41832</v>
-      </c>
-      <c r="E81" s="13">
-        <v>23</v>
+        <v>77</v>
+      </c>
+      <c r="C81" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D81" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E81" s="14">
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="C82" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D82" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E82" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B83" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -1826,7 +1891,7 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -1834,7 +1899,7 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -1842,63 +1907,63 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="4">
-        <v>13</v>
-      </c>
+      <c r="E86" s="4"/>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B87" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
+      <c r="E87" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="4">
-        <v>22</v>
-      </c>
+      <c r="E88" s="4"/>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
+      <c r="E89" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B90" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B91" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" s="16">
-        <v>44723</v>
-      </c>
-      <c r="D91" s="16">
-        <v>44723</v>
+      <c r="B91" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C91" s="21">
+        <v>45892</v>
+      </c>
+      <c r="D91" s="21">
+        <v>45892</v>
       </c>
       <c r="E91" s="4"/>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B92" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -1906,15 +1971,19 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="C93" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D93" s="16">
+        <v>44723</v>
+      </c>
       <c r="E93" s="4"/>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -1922,7 +1991,7 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B95" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -1930,7 +1999,7 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B96" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -1938,7 +2007,7 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -1946,7 +2015,7 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -1954,7 +2023,7 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -1962,7 +2031,7 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -1970,7 +2039,7 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -1978,17 +2047,19 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4">
-        <v>4</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C102" s="21">
+        <v>45689</v>
+      </c>
+      <c r="D102" s="21">
+        <v>45773</v>
+      </c>
+      <c r="E102" s="4"/>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -1996,77 +2067,73 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B105" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C105" s="16">
-        <v>44961</v>
-      </c>
-      <c r="D105" s="16">
-        <v>45038</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
       <c r="E105" s="4"/>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B106" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C106" s="8">
-        <v>45403</v>
-      </c>
-      <c r="D106" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E106" s="14">
-        <v>29</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B107" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C107" s="8">
-        <v>45346</v>
-      </c>
-      <c r="D107" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E107" s="14">
-        <v>10</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C107" s="16">
+        <v>44961</v>
+      </c>
+      <c r="D107" s="16">
+        <v>45038</v>
+      </c>
+      <c r="E107" s="4"/>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B108" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="C108" s="8">
+        <v>45403</v>
+      </c>
+      <c r="D108" s="8">
+        <v>45403</v>
+      </c>
+      <c r="E108" s="14">
+        <v>29</v>
+      </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B109" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C109" s="8">
-        <v>44961</v>
+        <v>45346</v>
       </c>
       <c r="D109" s="8">
-        <v>45080</v>
+        <v>45423</v>
       </c>
       <c r="E109" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B110" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -2074,15 +2141,21 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B111" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="C111" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D111" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E111" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B112" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -2090,7 +2163,7 @@
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B113" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -2098,7 +2171,7 @@
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B114" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -2106,61 +2179,57 @@
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B115" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C115" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D115" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E115" s="14">
-        <v>24</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B117" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
+      <c r="B117" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C117" s="21">
+        <v>45885</v>
+      </c>
+      <c r="D117" s="21">
+        <v>45885</v>
+      </c>
       <c r="E117" s="4"/>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B118" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C118" s="8">
-        <v>45556</v>
+        <v>45417</v>
       </c>
       <c r="D118" s="8">
-        <v>45556</v>
-      </c>
-      <c r="E118" s="4"/>
+        <v>45417</v>
+      </c>
+      <c r="E118" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B119" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C119" s="8">
-        <v>45273</v>
-      </c>
-      <c r="D119" s="8">
-        <v>45273</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
       <c r="E119" s="4"/>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -2168,23 +2237,31 @@
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
+        <v>115</v>
+      </c>
+      <c r="C121" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D121" s="8">
+        <v>45556</v>
+      </c>
       <c r="E121" s="4"/>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
+      <c r="B122" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C122" s="8">
+        <v>45273</v>
+      </c>
+      <c r="D122" s="8">
+        <v>45273</v>
+      </c>
       <c r="E122" s="4"/>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -2192,7 +2269,7 @@
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B124" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
@@ -2200,21 +2277,15 @@
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B125" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C125" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D125" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E125" s="13">
-        <v>24</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B126" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -2222,7 +2293,7 @@
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B127" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
@@ -2230,29 +2301,29 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B128" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="C128" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D128" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E128" s="13">
+        <v>24</v>
+      </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B129" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C129" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D129" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E129" s="13">
-        <v>1</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B130" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -2260,79 +2331,73 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B131" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C131" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D131" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E131" s="14">
-        <v>15</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B132" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="4">
-        <v>11</v>
+        <v>126</v>
+      </c>
+      <c r="C132" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D132" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E132" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B133" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C133" s="15">
-        <v>39760</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="C133" s="4"/>
       <c r="D133" s="4"/>
-      <c r="E133" s="4">
-        <v>3</v>
-      </c>
+      <c r="E133" s="4"/>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B134" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="C134" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D134" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E134" s="14">
+        <v>15</v>
+      </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B135" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C135" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D135" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E135" s="14">
-        <v>14</v>
+        <v>129</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4">
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B136" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C136" s="8">
-        <v>44811</v>
-      </c>
-      <c r="D136" s="8">
-        <v>44811</v>
-      </c>
-      <c r="E136" s="13">
-        <v>41</v>
+        <v>130</v>
+      </c>
+      <c r="C136" s="15">
+        <v>39760</v>
+      </c>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B137" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
@@ -2340,31 +2405,35 @@
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B138" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C138" s="12">
-        <v>44739</v>
+        <v>45003</v>
       </c>
       <c r="D138" s="12">
-        <v>44754</v>
-      </c>
-      <c r="E138" s="13">
-        <v>37</v>
+        <v>45080</v>
+      </c>
+      <c r="E138" s="14">
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B139" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
+        <v>133</v>
+      </c>
+      <c r="C139" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D139" s="8">
+        <v>44811</v>
+      </c>
       <c r="E139" s="13">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B140" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
@@ -2372,33 +2441,39 @@
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B141" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="C141" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D141" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E141" s="13">
+        <v>37</v>
+      </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
+      <c r="E142" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B143" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="4">
-        <v>18</v>
-      </c>
+      <c r="E143" s="4"/>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B144" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
@@ -2406,7 +2481,7 @@
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
@@ -2414,29 +2489,25 @@
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B146" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
+      <c r="E146" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B147" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C147" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D147" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E147" s="14">
-        <v>16</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B148" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
@@ -2444,7 +2515,7 @@
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
@@ -2452,15 +2523,21 @@
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B150" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
-      <c r="E150" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="C150" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D150" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E150" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B151" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
@@ -2468,7 +2545,7 @@
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B152" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
@@ -2476,7 +2553,7 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B153" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
@@ -2484,21 +2561,15 @@
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B154" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C154" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D154" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E154" s="14">
-        <v>18</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -2506,7 +2577,7 @@
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B156" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -2514,29 +2585,29 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B157" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C157" s="4"/>
-      <c r="D157" s="4"/>
-      <c r="E157" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="C157" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D157" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E157" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B158" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C158" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D158" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E158" s="13">
-        <v>42</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B159" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
@@ -2544,65 +2615,116 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B160" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
-      <c r="E160" s="4">
-        <v>6</v>
-      </c>
+      <c r="E160" s="4"/>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B161" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C161" s="4"/>
-      <c r="D161" s="4"/>
-      <c r="E161" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="C161" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D161" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E161" s="13">
+        <v>42</v>
+      </c>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B162" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-      <c r="E162" s="4">
-        <v>20</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C162" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D162" s="22">
+        <v>44688</v>
+      </c>
+      <c r="E162" s="4"/>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B163" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
-      <c r="E163" s="4"/>
+      <c r="E163" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B164" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C164" s="15">
-        <v>42350</v>
-      </c>
-      <c r="D164" s="12">
-        <v>42532</v>
-      </c>
-      <c r="E164" s="13">
-        <v>21</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C164" s="21">
+        <v>45494</v>
+      </c>
+      <c r="D164" s="21">
+        <v>45494</v>
+      </c>
+      <c r="E164" s="4"/>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B165" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
+      <c r="E165" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B167" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C167" s="15">
+        <v>42350</v>
+      </c>
+      <c r="D167" s="12">
+        <v>42532</v>
+      </c>
+      <c r="E167" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B168" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C168" s="22">
+        <v>44436</v>
+      </c>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B169" s="3" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B170" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C170" s="24">
+        <v>45917</v>
+      </c>
+      <c r="D170" s="24">
+        <v>45917</v>
       </c>
     </row>
   </sheetData>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\GitHub\Brumario\backend\src\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1AA86B-291A-4771-98BF-891D5C23A682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF1DF5-659E-4801-8B96-6F731E9ED80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t>Nombre</t>
   </si>
@@ -552,15 +553,17 @@
   </si>
   <si>
     <t>Zenobi, Laureano</t>
+  </si>
+  <si>
+    <t>Rodríguez, Marcelo Abel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -694,7 +697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -726,7 +729,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -738,7 +741,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -765,9 +768,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1049,17 +1060,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E170"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:E171"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.26953125" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1073,751 +1084,751 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="19" t="s">
+        <v>167</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C12" s="5">
         <v>45472</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D12" s="5">
         <v>45472</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E12" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="1" t="s">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C14" s="5">
         <v>45361</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D14" s="5">
         <v>45396</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E14" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B14" s="1" t="s">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C15" s="5">
         <v>45164</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D15" s="5">
         <v>45200</v>
       </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="1" t="s">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B16" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <v>44422</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D18" s="6">
         <v>44436</v>
       </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C19" s="5">
         <v>44793</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D19" s="5">
         <v>44807</v>
       </c>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="1" t="s">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C20" s="7">
         <v>45220</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D20" s="7">
         <v>45220</v>
       </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="1" t="s">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C24" s="8">
         <v>45346</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D24" s="8">
         <v>45423</v>
       </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="1" t="s">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="4">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="1" t="s">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C27" s="9">
         <v>44739</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D27" s="9">
         <v>44746</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E27" s="10">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="1" t="s">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C28" s="8">
         <v>45164</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D28" s="11">
         <v>45220</v>
       </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B28" s="1" t="s">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="12">
+      <c r="C32" s="4"/>
+      <c r="D32" s="12">
         <v>42161</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E32" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B32" s="1" t="s">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B33" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4">
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B34" s="1" t="s">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C35" s="8">
         <v>44758</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D35" s="8">
         <v>44758</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E35" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B36" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E37" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C45" s="8">
         <v>45395</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D45" s="8">
         <v>45423</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E45" s="14">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C47" s="12">
         <v>43652</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D47" s="12">
         <v>43722</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E47" s="13">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B47" s="1" t="s">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C49" s="15">
         <v>42294</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D49" s="12">
         <v>42294</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E49" s="13">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B49" s="1" t="s">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B50" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="4">
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B51" s="1" t="s">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C52" s="8">
         <v>45395</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D52" s="8">
         <v>45423</v>
       </c>
-      <c r="E51" s="14">
+      <c r="E52" s="14">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B52" s="1" t="s">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="12">
+      <c r="C53" s="4"/>
+      <c r="D53" s="12">
         <v>42161</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E53" s="13">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C54" s="9">
         <v>44739</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D54" s="9">
         <v>44746</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E54" s="10">
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B54" s="1" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C55" s="8">
         <v>43708</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D55" s="8">
         <v>44716</v>
       </c>
-      <c r="E54" s="13">
+      <c r="E55" s="13">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C56" s="8">
         <v>44961</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D56" s="8">
         <v>45038</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E56" s="13">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C57" s="8">
         <v>45346</v>
-      </c>
-      <c r="D56" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E56" s="14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B57" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C57" s="8">
-        <v>45374</v>
       </c>
       <c r="D57" s="8">
         <v>45423</v>
       </c>
-      <c r="E57" s="4"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E57" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="8">
+        <v>45374</v>
+      </c>
+      <c r="D58" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C60" s="9">
         <v>44226</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D60" s="9">
         <v>44436</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E60" s="10">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B60" s="1" t="s">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="12">
+      <c r="C62" s="4"/>
+      <c r="D62" s="12">
         <v>42161</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E62" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B62" s="1" t="s">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B63" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C67" s="11">
         <v>45255</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D67" s="11">
         <v>45255</v>
       </c>
-      <c r="E66" s="14">
+      <c r="E67" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B68" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C71" s="12">
         <v>43890</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D71" s="12">
         <v>44436</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E71" s="13">
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="s">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C72" s="8">
         <v>45361</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D72" s="8">
         <v>45403</v>
       </c>
-      <c r="E71" s="4"/>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B72" s="1" t="s">
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C73" s="8">
         <v>45417</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D73" s="8">
         <v>45417</v>
       </c>
-      <c r="E72" s="4"/>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B73" s="1" t="s">
+      <c r="E73" s="4"/>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B74" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B76" s="19" t="s">
-        <v>167</v>
+      <c r="E75" s="4"/>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E76" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="19" t="s">
         <v>168</v>
       </c>
@@ -1829,7 +1840,7 @@
       </c>
       <c r="E77" s="4"/>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
         <v>74</v>
       </c>
@@ -1837,7 +1848,7 @@
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
         <v>75</v>
       </c>
@@ -1845,7 +1856,7 @@
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>76</v>
       </c>
@@ -1853,7 +1864,7 @@
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
         <v>77</v>
       </c>
@@ -1867,7 +1878,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>78</v>
       </c>
@@ -1881,7 +1892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
         <v>79</v>
       </c>
@@ -1889,7 +1900,7 @@
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>80</v>
       </c>
@@ -1897,7 +1908,7 @@
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>81</v>
       </c>
@@ -1905,7 +1916,7 @@
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>82</v>
       </c>
@@ -1913,7 +1924,7 @@
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>83</v>
       </c>
@@ -1923,7 +1934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>84</v>
       </c>
@@ -1931,7 +1942,7 @@
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
         <v>85</v>
       </c>
@@ -1941,7 +1952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>86</v>
       </c>
@@ -1949,7 +1960,7 @@
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="19" t="s">
         <v>169</v>
       </c>
@@ -1961,7 +1972,7 @@
       </c>
       <c r="E91" s="4"/>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
         <v>87</v>
       </c>
@@ -1969,7 +1980,7 @@
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
         <v>88</v>
       </c>
@@ -1981,7 +1992,7 @@
       </c>
       <c r="E93" s="4"/>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
         <v>89</v>
       </c>
@@ -1989,7 +2000,7 @@
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
         <v>90</v>
       </c>
@@ -1997,7 +2008,7 @@
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
         <v>91</v>
       </c>
@@ -2005,7 +2016,7 @@
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
         <v>92</v>
       </c>
@@ -2013,7 +2024,7 @@
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
         <v>93</v>
       </c>
@@ -2021,7 +2032,7 @@
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
         <v>94</v>
       </c>
@@ -2029,7 +2040,7 @@
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
         <v>95</v>
       </c>
@@ -2037,7 +2048,7 @@
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
         <v>96</v>
       </c>
@@ -2045,7 +2056,7 @@
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
         <v>97</v>
       </c>
@@ -2057,7 +2068,7 @@
       </c>
       <c r="E102" s="4"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
         <v>98</v>
       </c>
@@ -2065,7 +2076,7 @@
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
         <v>99</v>
       </c>
@@ -2075,7 +2086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
         <v>100</v>
       </c>
@@ -2083,7 +2094,7 @@
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
         <v>101</v>
       </c>
@@ -2091,7 +2102,7 @@
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
         <v>102</v>
       </c>
@@ -2103,7 +2114,7 @@
       </c>
       <c r="E107" s="4"/>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
         <v>103</v>
       </c>
@@ -2117,7 +2128,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
         <v>104</v>
       </c>
@@ -2131,7 +2142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
         <v>105</v>
       </c>
@@ -2139,7 +2150,7 @@
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
         <v>106</v>
       </c>
@@ -2153,7 +2164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
         <v>107</v>
       </c>
@@ -2161,7 +2172,7 @@
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
         <v>108</v>
       </c>
@@ -2169,7 +2180,7 @@
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
         <v>109</v>
       </c>
@@ -2177,7 +2188,7 @@
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
         <v>110</v>
       </c>
@@ -2185,7 +2196,7 @@
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
         <v>111</v>
       </c>
@@ -2193,7 +2204,7 @@
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" s="19" t="s">
         <v>170</v>
       </c>
@@ -2205,7 +2216,7 @@
       </c>
       <c r="E117" s="4"/>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
         <v>112</v>
       </c>
@@ -2219,7 +2230,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
         <v>113</v>
       </c>
@@ -2227,7 +2238,7 @@
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
         <v>114</v>
       </c>
@@ -2235,7 +2246,7 @@
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
         <v>115</v>
       </c>
@@ -2247,7 +2258,7 @@
       </c>
       <c r="E121" s="4"/>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" s="19" t="s">
         <v>116</v>
       </c>
@@ -2259,7 +2270,7 @@
       </c>
       <c r="E122" s="4"/>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
         <v>117</v>
       </c>
@@ -2267,7 +2278,7 @@
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
         <v>118</v>
       </c>
@@ -2275,7 +2286,7 @@
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
         <v>119</v>
       </c>
@@ -2283,7 +2294,7 @@
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
         <v>120</v>
       </c>
@@ -2291,7 +2302,7 @@
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
         <v>121</v>
       </c>
@@ -2299,7 +2310,7 @@
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
         <v>122</v>
       </c>
@@ -2313,7 +2324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
         <v>123</v>
       </c>
@@ -2321,7 +2332,7 @@
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
         <v>124</v>
       </c>
@@ -2329,7 +2340,7 @@
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
         <v>125</v>
       </c>
@@ -2337,7 +2348,7 @@
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
         <v>126</v>
       </c>
@@ -2351,7 +2362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
         <v>127</v>
       </c>
@@ -2359,7 +2370,7 @@
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
         <v>128</v>
       </c>
@@ -2373,7 +2384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
         <v>129</v>
       </c>
@@ -2383,7 +2394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
         <v>130</v>
       </c>
@@ -2395,7 +2406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
         <v>131</v>
       </c>
@@ -2403,7 +2414,7 @@
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
         <v>132</v>
       </c>
@@ -2417,7 +2428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
         <v>133</v>
       </c>
@@ -2431,303 +2442,319 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B140" s="1" t="s">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B140" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C140" s="24">
+        <v>45993</v>
+      </c>
+      <c r="D140" s="24">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B141" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B142" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C141" s="12">
+      <c r="C142" s="12">
         <v>44739</v>
       </c>
-      <c r="D141" s="12">
+      <c r="D142" s="12">
         <v>44754</v>
       </c>
-      <c r="E141" s="13">
+      <c r="E142" s="13">
         <v>37</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B143" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="13">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B143" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E143" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
-      <c r="E146" s="4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E146" s="4"/>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="4"/>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E147" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B151" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C150" s="18">
+      <c r="C151" s="18">
         <v>45097</v>
       </c>
-      <c r="D150" s="18">
+      <c r="D151" s="18">
         <v>45097</v>
       </c>
-      <c r="E150" s="14">
+      <c r="E151" s="14">
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B152" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
-    </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B158" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C157" s="11">
+      <c r="C158" s="11">
         <v>45423</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D158" s="11">
         <v>45423</v>
       </c>
-      <c r="E157" s="14">
+      <c r="E158" s="14">
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B158" s="1" t="s">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B159" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
-    </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B162" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C161" s="17">
+      <c r="C162" s="17">
         <v>44660</v>
       </c>
-      <c r="D161" s="17">
+      <c r="D162" s="17">
         <v>44674</v>
       </c>
-      <c r="E161" s="13">
+      <c r="E162" s="13">
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B162" s="1" t="s">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B163" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C162" s="22">
+      <c r="C163" s="22">
         <v>44688</v>
       </c>
-      <c r="D162" s="22">
+      <c r="D163" s="22">
         <v>44688</v>
       </c>
-      <c r="E162" s="4"/>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B163" s="1" t="s">
+      <c r="E163" s="4"/>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B164" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-      <c r="E163" s="4">
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B164" s="1" t="s">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B165" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C164" s="21">
+      <c r="C165" s="21">
         <v>45494</v>
       </c>
-      <c r="D164" s="21">
+      <c r="D165" s="21">
         <v>45494</v>
       </c>
-      <c r="E164" s="4"/>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B165" s="1" t="s">
+      <c r="E165" s="4"/>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B166" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B166" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
-      <c r="E166" s="4"/>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E166" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B168" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C167" s="15">
+      <c r="C168" s="15">
         <v>42350</v>
       </c>
-      <c r="D167" s="12">
+      <c r="D168" s="12">
         <v>42532</v>
       </c>
-      <c r="E167" s="13">
+      <c r="E168" s="13">
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B168" s="1" t="s">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B169" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C168" s="22">
+      <c r="C169" s="22">
         <v>44436</v>
       </c>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B169" s="3" t="s">
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+    </row>
+    <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B170" s="26" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B170" s="23" t="s">
+      <c r="C170" s="28"/>
+      <c r="D170" s="28"/>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B171" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C170" s="24">
+      <c r="C171" s="27">
         <v>45917</v>
       </c>
-      <c r="D170" s="24">
+      <c r="D171" s="27">
         <v>45917</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E171">
+    <sortCondition ref="B2:B171"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF1DF5-659E-4801-8B96-6F731E9ED80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF714FA-1573-4FAC-AEB7-EB72515F5153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t>Nombre</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>Rodríguez, Marcelo Abel</t>
+  </si>
+  <si>
+    <t>Primo de Ale</t>
   </si>
 </sst>
 </file>
@@ -697,7 +700,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -778,7 +781,13 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1060,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E171"/>
+  <dimension ref="B2:E172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -2371,131 +2380,131 @@
       <c r="E133" s="4"/>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B134" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C134" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D134" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E134" s="14">
-        <v>15</v>
+      <c r="B134" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" s="24">
+        <v>45982</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="4">
-        <v>11</v>
+        <v>128</v>
+      </c>
+      <c r="C135" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D135" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E135" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C136" s="15">
-        <v>39760</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C137" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="C137" s="15">
+        <v>39760</v>
+      </c>
       <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
+      <c r="E137" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C138" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D138" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E138" s="14">
-        <v>14</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C139" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D139" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E139" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B140" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C140" s="8">
         <v>44811</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D140" s="8">
         <v>44811</v>
       </c>
-      <c r="E139" s="13">
+      <c r="E140" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B140" s="25" t="s">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B141" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="C140" s="24">
+      <c r="C141" s="24">
         <v>45993</v>
       </c>
-      <c r="D140" s="24">
+      <c r="D141" s="24">
         <v>45993</v>
       </c>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B141" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C142" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D142" s="12">
-        <v>44754</v>
-      </c>
-      <c r="E142" s="13">
-        <v>37</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="C143" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D143" s="12">
+        <v>44754</v>
+      </c>
       <c r="E143" s="13">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
-      <c r="E144" s="4"/>
+      <c r="E144" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
@@ -2503,7 +2512,7 @@
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
@@ -2511,25 +2520,25 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="4">
-        <v>18</v>
-      </c>
+      <c r="E147" s="4"/>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
+      <c r="E148" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
@@ -2537,7 +2546,7 @@
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
@@ -2545,29 +2554,29 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C151" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D151" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E151" s="14">
-        <v>16</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="C152" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D152" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E152" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
@@ -2575,7 +2584,7 @@
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -2583,7 +2592,7 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -2591,7 +2600,7 @@
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -2599,7 +2608,7 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2607,29 +2616,29 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C158" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D158" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E158" s="14">
-        <v>18</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="C159" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D159" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E159" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -2637,7 +2646,7 @@
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2645,115 +2654,123 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C162" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D162" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E162" s="13">
-        <v>42</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C163" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D163" s="22">
-        <v>44688</v>
-      </c>
-      <c r="E163" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="C163" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D163" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E163" s="13">
+        <v>42</v>
+      </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="4">
-        <v>6</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C164" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D164" s="22">
+        <v>44688</v>
+      </c>
+      <c r="E164" s="4"/>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C165" s="21">
-        <v>45494</v>
-      </c>
-      <c r="D165" s="21">
-        <v>45494</v>
-      </c>
-      <c r="E165" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4">
-        <v>20</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C166" s="21">
+        <v>45494</v>
+      </c>
+      <c r="D166" s="21">
+        <v>45494</v>
+      </c>
+      <c r="E166" s="4"/>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
-      <c r="E167" s="4"/>
+      <c r="E167" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C168" s="15">
-        <v>42350</v>
-      </c>
-      <c r="D168" s="12">
-        <v>42532</v>
-      </c>
-      <c r="E168" s="13">
-        <v>21</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C169" s="22">
-        <v>44436</v>
-      </c>
-      <c r="D169" s="4"/>
-      <c r="E169" s="4"/>
+        <v>161</v>
+      </c>
+      <c r="C169" s="15">
+        <v>42350</v>
+      </c>
+      <c r="D169" s="12">
+        <v>42532</v>
+      </c>
+      <c r="E169" s="13">
+        <v>21</v>
+      </c>
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C170" s="29">
+        <v>44436</v>
+      </c>
+      <c r="D170" s="30"/>
+      <c r="E170" s="4"/>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B171" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C170" s="28"/>
-      <c r="D170" s="28"/>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B171" s="23" t="s">
+      <c r="C171" s="28"/>
+      <c r="D171" s="28"/>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B172" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C171" s="27">
+      <c r="C172" s="27">
         <v>45917</v>
       </c>
-      <c r="D171" s="27">
+      <c r="D172" s="27">
         <v>45917</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E171">
-    <sortCondition ref="B2:B171"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E172">
+    <sortCondition ref="B2:B172"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF714FA-1573-4FAC-AEB7-EB72515F5153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D680A865-04EF-4ECC-A33E-5AE9B273C1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t>Nombre</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>Primo de Ale</t>
+  </si>
+  <si>
+    <t>Dimodica, Lucas</t>
   </si>
 </sst>
 </file>
@@ -700,7 +703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -782,11 +785,17 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1069,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E172"/>
+  <dimension ref="B2:E173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -1704,16 +1713,16 @@
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
+      <c r="B63" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" s="24">
+        <v>46060</v>
+      </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -1721,7 +1730,7 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -1729,7 +1738,7 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
@@ -1737,29 +1746,29 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C67" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D67" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E67" s="14">
-        <v>8</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="C68" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D68" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E68" s="14">
+        <v>8</v>
+      </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -1767,7 +1776,7 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -1775,53 +1784,53 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C71" s="12">
-        <v>43890</v>
-      </c>
-      <c r="D71" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E71" s="13">
-        <v>27</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C72" s="8">
-        <v>45361</v>
-      </c>
-      <c r="D72" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E72" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="C72" s="12">
+        <v>43890</v>
+      </c>
+      <c r="D72" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E72" s="13">
+        <v>27</v>
+      </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C73" s="8">
-        <v>45417</v>
+        <v>45361</v>
       </c>
       <c r="D73" s="8">
-        <v>45417</v>
+        <v>45403</v>
       </c>
       <c r="E73" s="4"/>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="C74" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D74" s="8">
+        <v>45417</v>
+      </c>
       <c r="E74" s="4"/>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -1829,37 +1838,37 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="4">
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B77" s="19" t="s">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B78" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C77" s="20">
+      <c r="C78" s="20">
         <v>45913</v>
       </c>
-      <c r="D77" s="20">
+      <c r="D78" s="20">
         <v>45913</v>
       </c>
-      <c r="E77" s="4"/>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B78" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
       <c r="E78" s="4"/>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -1867,7 +1876,7 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -1875,43 +1884,43 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C81" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D81" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E81" s="14">
-        <v>31</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C82" s="12">
-        <v>41832</v>
-      </c>
-      <c r="D82" s="12">
-        <v>41832</v>
-      </c>
-      <c r="E82" s="13">
-        <v>23</v>
+        <v>77</v>
+      </c>
+      <c r="C82" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D82" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E82" s="14">
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="C83" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D83" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E83" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -1919,7 +1928,7 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -1927,7 +1936,7 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -1935,83 +1944,83 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
-      <c r="E87" s="4">
-        <v>13</v>
-      </c>
+      <c r="E87" s="4"/>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+      <c r="E88" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
-      <c r="E89" s="4">
-        <v>22</v>
-      </c>
+      <c r="E89" s="4"/>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
+      <c r="E90" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B91" s="19" t="s">
+      <c r="B91" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B92" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C91" s="21">
+      <c r="C92" s="21">
         <v>45892</v>
       </c>
-      <c r="D91" s="21">
+      <c r="D92" s="21">
         <v>45892</v>
       </c>
-      <c r="E91" s="4"/>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B92" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
       <c r="E92" s="4"/>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" s="16">
-        <v>44723</v>
-      </c>
-      <c r="D93" s="16">
-        <v>44723</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
       <c r="E93" s="4"/>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="C94" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D94" s="16">
+        <v>44723</v>
+      </c>
       <c r="E94" s="4"/>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -2019,7 +2028,7 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -2027,7 +2036,7 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -2035,7 +2044,7 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -2043,7 +2052,7 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -2051,7 +2060,7 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -2059,7 +2068,7 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -2067,45 +2076,45 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C102" s="21">
-        <v>45689</v>
-      </c>
-      <c r="D102" s="21">
-        <v>45773</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
       <c r="E102" s="4"/>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
+        <v>97</v>
+      </c>
+      <c r="C103" s="21">
+        <v>45689</v>
+      </c>
+      <c r="D103" s="21">
+        <v>45773</v>
+      </c>
       <c r="E103" s="4"/>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
-      <c r="E104" s="4">
-        <v>4</v>
-      </c>
+      <c r="E104" s="4"/>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
+      <c r="E105" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -2113,77 +2122,77 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C107" s="16">
-        <v>44961</v>
-      </c>
-      <c r="D107" s="16">
-        <v>45038</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
       <c r="E107" s="4"/>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C108" s="8">
-        <v>45403</v>
-      </c>
-      <c r="D108" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E108" s="14">
-        <v>29</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C108" s="16">
+        <v>44961</v>
+      </c>
+      <c r="D108" s="16">
+        <v>45038</v>
+      </c>
+      <c r="E108" s="4"/>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C109" s="8">
-        <v>45346</v>
+        <v>45403</v>
       </c>
       <c r="D109" s="8">
-        <v>45423</v>
+        <v>45403</v>
       </c>
       <c r="E109" s="14">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
+        <v>104</v>
+      </c>
+      <c r="C110" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D110" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E110" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C111" s="8">
-        <v>44961</v>
-      </c>
-      <c r="D111" s="8">
-        <v>45080</v>
-      </c>
-      <c r="E111" s="14">
-        <v>3</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="C112" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D112" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E112" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -2191,7 +2200,7 @@
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -2199,7 +2208,7 @@
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -2207,49 +2216,49 @@
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B118" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="C117" s="21">
+      <c r="C118" s="21">
         <v>45885</v>
       </c>
-      <c r="D117" s="21">
+      <c r="D118" s="21">
         <v>45885</v>
       </c>
-      <c r="E117" s="4"/>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B118" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C118" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D118" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E118" s="14">
-        <v>24</v>
-      </c>
+      <c r="E118" s="4"/>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="C119" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D119" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E119" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -2257,39 +2266,39 @@
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B122" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C121" s="8">
+      <c r="C122" s="8">
         <v>45556</v>
       </c>
-      <c r="D121" s="8">
+      <c r="D122" s="8">
         <v>45556</v>
       </c>
-      <c r="E121" s="4"/>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B122" s="19" t="s">
+      <c r="E122" s="4"/>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B123" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C123" s="8">
         <v>45273</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D123" s="8">
         <v>45273</v>
       </c>
-      <c r="E122" s="4"/>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B123" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
       <c r="E123" s="4"/>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
@@ -2297,7 +2306,7 @@
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
@@ -2305,7 +2314,7 @@
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -2313,7 +2322,7 @@
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
@@ -2321,29 +2330,29 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C128" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D128" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E128" s="13">
-        <v>24</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="C129" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D129" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E129" s="13">
+        <v>24</v>
+      </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -2351,7 +2360,7 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -2359,160 +2368,160 @@
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C132" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D132" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E132" s="13">
-        <v>1</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C133" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D133" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E133" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B134" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B134" s="25" t="s">
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B135" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C134" s="24">
+      <c r="C135" s="24">
         <v>45982</v>
-      </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B135" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C135" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D135" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E135" s="14">
-        <v>15</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4">
-        <v>11</v>
+        <v>128</v>
+      </c>
+      <c r="C136" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D136" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E136" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C137" s="15">
-        <v>39760</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C138" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="C138" s="15">
+        <v>39760</v>
+      </c>
       <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
+      <c r="E138" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C139" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D139" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E139" s="14">
-        <v>14</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C140" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D140" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E140" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B141" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C141" s="8">
         <v>44811</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D141" s="8">
         <v>44811</v>
       </c>
-      <c r="E140" s="13">
+      <c r="E141" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B141" s="25" t="s">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B142" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="C141" s="24">
+      <c r="C142" s="24">
         <v>45993</v>
       </c>
-      <c r="D141" s="24">
+      <c r="D142" s="24">
         <v>45993</v>
       </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B142" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C143" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D143" s="12">
-        <v>44754</v>
-      </c>
-      <c r="E143" s="13">
-        <v>37</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="C144" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D144" s="12">
+        <v>44754</v>
+      </c>
       <c r="E144" s="13">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
+      <c r="E145" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
@@ -2520,7 +2529,7 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
@@ -2528,25 +2537,25 @@
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="4">
-        <v>18</v>
-      </c>
+      <c r="E148" s="4"/>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
+      <c r="E149" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
@@ -2554,7 +2563,7 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
@@ -2562,29 +2571,29 @@
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C152" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D152" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E152" s="14">
-        <v>16</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="C153" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D153" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E153" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -2592,7 +2601,7 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -2600,7 +2609,7 @@
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -2608,7 +2617,7 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2616,7 +2625,7 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -2624,29 +2633,29 @@
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C159" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D159" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E159" s="14">
-        <v>18</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="C160" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D160" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E160" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2654,7 +2663,7 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
@@ -2662,115 +2671,123 @@
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C163" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D163" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E163" s="13">
-        <v>42</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C164" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D164" s="22">
-        <v>44688</v>
-      </c>
-      <c r="E164" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="C164" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D164" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E164" s="13">
+        <v>42</v>
+      </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4">
-        <v>6</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C165" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D165" s="22">
+        <v>44688</v>
+      </c>
+      <c r="E165" s="4"/>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C166" s="21">
-        <v>45494</v>
-      </c>
-      <c r="D166" s="21">
-        <v>45494</v>
-      </c>
-      <c r="E166" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-      <c r="E167" s="4">
-        <v>20</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C167" s="21">
+        <v>45494</v>
+      </c>
+      <c r="D167" s="21">
+        <v>45494</v>
+      </c>
+      <c r="E167" s="4"/>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
+      <c r="E168" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C169" s="15">
-        <v>42350</v>
-      </c>
-      <c r="D169" s="12">
-        <v>42532</v>
-      </c>
-      <c r="E169" s="13">
-        <v>21</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C170" s="29">
-        <v>44436</v>
-      </c>
-      <c r="D170" s="30"/>
-      <c r="E170" s="4"/>
+        <v>161</v>
+      </c>
+      <c r="C170" s="30">
+        <v>42350</v>
+      </c>
+      <c r="D170" s="32">
+        <v>42532</v>
+      </c>
+      <c r="E170" s="13">
+        <v>21</v>
+      </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C171" s="29">
+        <v>44436</v>
+      </c>
+      <c r="D171" s="31"/>
+      <c r="E171" s="4"/>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B172" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C171" s="28"/>
-      <c r="D171" s="28"/>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B172" s="23" t="s">
+      <c r="C172" s="28"/>
+      <c r="D172" s="28"/>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B173" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="27">
+      <c r="C173" s="27">
         <v>45917</v>
       </c>
-      <c r="D172" s="27">
+      <c r="D173" s="27">
         <v>45917</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E172">
-    <sortCondition ref="B2:B172"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E173">
+    <sortCondition ref="B2:B173"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D680A865-04EF-4ECC-A33E-5AE9B273C1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E556BA39-2AF1-4A4E-BC30-777AF94AC4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>Nombre</t>
   </si>
@@ -562,6 +562,12 @@
   </si>
   <si>
     <t>Dimodica, Lucas</t>
+  </si>
+  <si>
+    <t>Matías, de Chaco 4</t>
+  </si>
+  <si>
+    <t>Matías, de Chaco 6</t>
   </si>
 </sst>
 </file>
@@ -703,7 +709,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -788,13 +794,19 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1078,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E173"/>
+  <dimension ref="B2:E175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -2103,96 +2115,96 @@
       <c r="E104" s="4"/>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B105" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4">
-        <v>4</v>
+      <c r="B105" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C105" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D105" s="27">
+        <v>46183</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B106" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
+      <c r="B106" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C106" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D106" s="27">
+        <v>46183</v>
+      </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
+      <c r="E107" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C108" s="16">
-        <v>44961</v>
-      </c>
-      <c r="D108" s="16">
-        <v>45038</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
       <c r="E108" s="4"/>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C109" s="8">
-        <v>45403</v>
-      </c>
-      <c r="D109" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E109" s="14">
-        <v>29</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C110" s="8">
-        <v>45346</v>
-      </c>
-      <c r="D110" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E110" s="14">
-        <v>10</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C110" s="16">
+        <v>44961</v>
+      </c>
+      <c r="D110" s="16">
+        <v>45038</v>
+      </c>
+      <c r="E110" s="4"/>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="C111" s="8">
+        <v>45403</v>
+      </c>
+      <c r="D111" s="8">
+        <v>45403</v>
+      </c>
+      <c r="E111" s="14">
+        <v>29</v>
+      </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C112" s="8">
-        <v>44961</v>
+        <v>45346</v>
       </c>
       <c r="D112" s="8">
-        <v>45080</v>
+        <v>45423</v>
       </c>
       <c r="E112" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -2200,15 +2212,21 @@
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="C114" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D114" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E114" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -2216,7 +2234,7 @@
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -2224,97 +2242,97 @@
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B118" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C118" s="21">
-        <v>45885</v>
-      </c>
-      <c r="D118" s="21">
-        <v>45885</v>
-      </c>
+      <c r="B118" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
       <c r="E118" s="4"/>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C119" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D119" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E119" s="14">
-        <v>24</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B120" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
+      <c r="B120" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C120" s="21">
+        <v>45885</v>
+      </c>
+      <c r="D120" s="21">
+        <v>45885</v>
+      </c>
       <c r="E120" s="4"/>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="C121" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D121" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E121" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C122" s="8">
-        <v>45556</v>
-      </c>
-      <c r="D122" s="8">
-        <v>45556</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
       <c r="E122" s="4"/>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B123" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="C123" s="8">
-        <v>45273</v>
-      </c>
-      <c r="D123" s="8">
-        <v>45273</v>
-      </c>
+      <c r="B123" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
       <c r="E123" s="4"/>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
+        <v>115</v>
+      </c>
+      <c r="C124" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D124" s="8">
+        <v>45556</v>
+      </c>
       <c r="E124" s="4"/>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B125" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
+      <c r="B125" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C125" s="8">
+        <v>45273</v>
+      </c>
+      <c r="D125" s="8">
+        <v>45273</v>
+      </c>
       <c r="E125" s="4"/>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -2322,7 +2340,7 @@
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
@@ -2330,7 +2348,7 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
@@ -2338,21 +2356,15 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C129" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D129" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E129" s="13">
-        <v>24</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -2360,15 +2372,21 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="C131" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D131" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E131" s="13">
+        <v>24</v>
+      </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -2376,168 +2394,168 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C133" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D133" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E133" s="13">
-        <v>1</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B135" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="C135" s="24">
-        <v>45982</v>
+      <c r="B135" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C135" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D135" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E135" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C136" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D136" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E136" s="14">
-        <v>15</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B137" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4">
-        <v>11</v>
+      <c r="B137" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C137" s="24">
+        <v>45982</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C138" s="15">
-        <v>39760</v>
-      </c>
-      <c r="D138" s="4"/>
-      <c r="E138" s="4">
-        <v>3</v>
+        <v>128</v>
+      </c>
+      <c r="C138" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D138" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E138" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
+      <c r="E139" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C140" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D140" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E140" s="14">
-        <v>14</v>
+        <v>130</v>
+      </c>
+      <c r="C140" s="15">
+        <v>39760</v>
+      </c>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C141" s="8">
-        <v>44811</v>
-      </c>
-      <c r="D141" s="8">
-        <v>44811</v>
-      </c>
-      <c r="E141" s="13">
-        <v>41</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B142" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C142" s="24">
-        <v>45993</v>
-      </c>
-      <c r="D142" s="24">
-        <v>45993</v>
+      <c r="B142" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C142" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D142" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E142" s="14">
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
+        <v>133</v>
+      </c>
+      <c r="C143" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D143" s="8">
+        <v>44811</v>
+      </c>
+      <c r="E143" s="13">
+        <v>41</v>
+      </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B144" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C144" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D144" s="12">
-        <v>44754</v>
-      </c>
-      <c r="E144" s="13">
-        <v>37</v>
+      <c r="B144" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" s="24">
+        <v>45993</v>
+      </c>
+      <c r="D144" s="24">
+        <v>45993</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
-      <c r="E145" s="13">
-        <v>29</v>
-      </c>
+      <c r="E145" s="4"/>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="C146" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D146" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E146" s="13">
+        <v>37</v>
+      </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="4"/>
+      <c r="E147" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
@@ -2545,17 +2563,15 @@
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
-      <c r="E149" s="4">
-        <v>18</v>
-      </c>
+      <c r="E149" s="4"/>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
@@ -2563,15 +2579,17 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
+      <c r="E151" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
@@ -2579,21 +2597,15 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C153" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D153" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E153" s="14">
-        <v>16</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -2601,15 +2613,21 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="C155" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D155" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E155" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -2617,7 +2635,7 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2625,7 +2643,7 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -2633,7 +2651,7 @@
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
@@ -2641,21 +2659,15 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C160" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D160" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E160" s="14">
-        <v>18</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2663,15 +2675,21 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-      <c r="E162" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="C162" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D162" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E162" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
@@ -2679,115 +2697,131 @@
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C164" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D164" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E164" s="13">
-        <v>42</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4"/>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C165" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D165" s="22">
-        <v>44688</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
       <c r="E165" s="4"/>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4">
-        <v>6</v>
+        <v>155</v>
+      </c>
+      <c r="C166" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D166" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E166" s="13">
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C167" s="21">
-        <v>45494</v>
-      </c>
-      <c r="D167" s="21">
-        <v>45494</v>
+        <v>156</v>
+      </c>
+      <c r="C167" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D167" s="22">
+        <v>44688</v>
       </c>
       <c r="E167" s="4"/>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C169" s="4"/>
-      <c r="D169" s="4"/>
+        <v>158</v>
+      </c>
+      <c r="C169" s="21">
+        <v>45494</v>
+      </c>
+      <c r="D169" s="21">
+        <v>45494</v>
+      </c>
       <c r="E169" s="4"/>
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C170" s="30">
-        <v>42350</v>
-      </c>
-      <c r="D170" s="32">
-        <v>42532</v>
-      </c>
-      <c r="E170" s="13">
-        <v>21</v>
+        <v>159</v>
+      </c>
+      <c r="C170" s="33"/>
+      <c r="D170" s="33"/>
+      <c r="E170" s="4">
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C171" s="29">
-        <v>44436</v>
-      </c>
-      <c r="D171" s="31"/>
+        <v>160</v>
+      </c>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
       <c r="E171" s="4"/>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="C172" s="32">
+        <v>42350</v>
+      </c>
+      <c r="D172" s="34">
+        <v>42532</v>
+      </c>
+      <c r="E172" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B173" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C173" s="29">
+        <v>44436</v>
+      </c>
+      <c r="D173" s="30"/>
+      <c r="E173" s="4"/>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B174" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C172" s="28"/>
-      <c r="D172" s="28"/>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B173" s="23" t="s">
+      <c r="C174" s="28"/>
+      <c r="D174" s="28"/>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B175" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C173" s="27">
+      <c r="C175" s="27">
         <v>45917</v>
       </c>
-      <c r="D173" s="27">
+      <c r="D175" s="27">
         <v>45917</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E173">
-    <sortCondition ref="B2:B173"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E175">
+    <sortCondition ref="B2:B175"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E556BA39-2AF1-4A4E-BC30-777AF94AC4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F32F9A9-2FEA-458D-8254-C55C30DE6F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,10 +564,10 @@
     <t>Dimodica, Lucas</t>
   </si>
   <si>
-    <t>Matías, de Chaco 4</t>
-  </si>
-  <si>
-    <t>Matías, de Chaco 6</t>
+    <t>Fernández, Matías</t>
+  </si>
+  <si>
+    <t>González, Matías</t>
   </si>
 </sst>
 </file>
@@ -1779,16 +1779,19 @@
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
+      <c r="B69" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C69" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D69" s="27">
+        <v>46183</v>
+      </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -1796,7 +1799,7 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -1804,53 +1807,53 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C72" s="12">
-        <v>43890</v>
-      </c>
-      <c r="D72" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E72" s="13">
-        <v>27</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C73" s="8">
-        <v>45361</v>
-      </c>
-      <c r="D73" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E73" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="C73" s="12">
+        <v>43890</v>
+      </c>
+      <c r="D73" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E73" s="13">
+        <v>27</v>
+      </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C74" s="8">
-        <v>45417</v>
+        <v>45361</v>
       </c>
       <c r="D74" s="8">
-        <v>45417</v>
+        <v>45403</v>
       </c>
       <c r="E74" s="4"/>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="C75" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D75" s="8">
+        <v>45417</v>
+      </c>
       <c r="E75" s="4"/>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -1858,97 +1861,100 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="4">
+      <c r="E77" s="4"/>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B78" s="19" t="s">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B79" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C78" s="20">
+      <c r="C79" s="20">
         <v>45913</v>
       </c>
-      <c r="D78" s="20">
+      <c r="D79" s="20">
         <v>45913</v>
       </c>
-      <c r="E78" s="4"/>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B79" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
       <c r="E79" s="4"/>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B81" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
+      <c r="B81" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D81" s="27">
+        <v>46183</v>
+      </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C82" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D82" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E82" s="14">
-        <v>31</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C83" s="12">
-        <v>41832</v>
-      </c>
-      <c r="D83" s="12">
-        <v>41832</v>
-      </c>
-      <c r="E83" s="13">
-        <v>23</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="C84" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D84" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E84" s="14">
+        <v>31</v>
+      </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="C85" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D85" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E85" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -1956,7 +1962,7 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -1964,17 +1970,15 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="4">
-        <v>13</v>
-      </c>
+      <c r="E88" s="4"/>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -1982,57 +1986,55 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B92" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C92" s="21">
-        <v>45892</v>
-      </c>
-      <c r="D92" s="21">
-        <v>45892</v>
-      </c>
-      <c r="E92" s="4"/>
+      <c r="B92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B94" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" s="16">
-        <v>44723</v>
-      </c>
-      <c r="D94" s="16">
-        <v>44723</v>
+      <c r="B94" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C94" s="21">
+        <v>45892</v>
+      </c>
+      <c r="D94" s="21">
+        <v>45892</v>
       </c>
       <c r="E94" s="4"/>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -2040,15 +2042,19 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="C96" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D96" s="16">
+        <v>44723</v>
+      </c>
       <c r="E96" s="4"/>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -2056,7 +2062,7 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -2064,7 +2070,7 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -2072,7 +2078,7 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -2080,7 +2086,7 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -2088,7 +2094,7 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -2096,45 +2102,39 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C103" s="21">
-        <v>45689</v>
-      </c>
-      <c r="D103" s="21">
-        <v>45773</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
       <c r="E103" s="4"/>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B105" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C105" s="27">
-        <v>46183</v>
-      </c>
-      <c r="D105" s="27">
-        <v>46183</v>
-      </c>
+      <c r="B105" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C105" s="21">
+        <v>45689</v>
+      </c>
+      <c r="D105" s="21">
+        <v>45773</v>
+      </c>
+      <c r="E105" s="4"/>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B106" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C106" s="27">
-        <v>46183</v>
-      </c>
-      <c r="D106" s="27">
-        <v>46183</v>
-      </c>
+      <c r="B106" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
@@ -2821,7 +2821,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E175">
-    <sortCondition ref="B2:B175"/>
+    <sortCondition ref="B3:B175"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F32F9A9-2FEA-458D-8254-C55C30DE6F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F2D64B-E5FB-43EB-8F85-04E6B130F494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Nombre</t>
   </si>
@@ -568,6 +568,12 @@
   </si>
   <si>
     <t>González, Matías</t>
+  </si>
+  <si>
+    <t>Nicolás, de Pucho</t>
+  </si>
+  <si>
+    <t>Zenobi, Thiago</t>
   </si>
 </sst>
 </file>
@@ -709,7 +715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -803,11 +809,14 @@
     <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1090,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E175"/>
+  <dimension ref="B2:E177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -2257,50 +2266,50 @@
       <c r="E118" s="4"/>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C119" s="24">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B120" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B120" s="19" t="s">
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B121" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="C120" s="21">
+      <c r="C121" s="21">
         <v>45885</v>
       </c>
-      <c r="D120" s="21">
+      <c r="D121" s="21">
         <v>45885</v>
       </c>
-      <c r="E120" s="4"/>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B121" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C121" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D121" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E121" s="14">
-        <v>24</v>
-      </c>
+      <c r="E121" s="4"/>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="C122" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D122" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E122" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -2308,39 +2317,39 @@
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B125" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C125" s="8">
         <v>45556</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D125" s="8">
         <v>45556</v>
       </c>
-      <c r="E124" s="4"/>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B125" s="19" t="s">
+      <c r="E125" s="4"/>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B126" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C126" s="8">
         <v>45273</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D126" s="8">
         <v>45273</v>
       </c>
-      <c r="E125" s="4"/>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B126" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
       <c r="E126" s="4"/>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
@@ -2348,7 +2357,7 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
@@ -2356,7 +2365,7 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
@@ -2364,7 +2373,7 @@
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -2372,29 +2381,29 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C131" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D131" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E131" s="13">
-        <v>24</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="C132" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D132" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E132" s="13">
+        <v>24</v>
+      </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
@@ -2402,7 +2411,7 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
@@ -2410,160 +2419,160 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C135" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D135" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E135" s="13">
-        <v>1</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C136" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D136" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E136" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B137" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4"/>
-    </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B137" s="25" t="s">
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B138" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C137" s="24">
+      <c r="C138" s="24">
         <v>45982</v>
-      </c>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B138" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C138" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D138" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E138" s="14">
-        <v>15</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="4">
-        <v>11</v>
+        <v>128</v>
+      </c>
+      <c r="C139" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D139" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E139" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C140" s="15">
-        <v>39760</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C141" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="C141" s="15">
+        <v>39760</v>
+      </c>
       <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
+      <c r="E141" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C142" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D142" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E142" s="14">
-        <v>14</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C143" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D143" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E143" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B144" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C143" s="8">
+      <c r="C144" s="8">
         <v>44811</v>
       </c>
-      <c r="D143" s="8">
+      <c r="D144" s="8">
         <v>44811</v>
       </c>
-      <c r="E143" s="13">
+      <c r="E144" s="13">
         <v>41</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B144" s="25" t="s">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B145" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="C144" s="24">
+      <c r="C145" s="24">
         <v>45993</v>
       </c>
-      <c r="D144" s="24">
+      <c r="D145" s="24">
         <v>45993</v>
       </c>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B145" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C146" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D146" s="12">
-        <v>44754</v>
-      </c>
-      <c r="E146" s="13">
-        <v>37</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C147" s="4"/>
-      <c r="D147" s="4"/>
+        <v>135</v>
+      </c>
+      <c r="C147" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D147" s="12">
+        <v>44754</v>
+      </c>
       <c r="E147" s="13">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
+      <c r="E148" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
@@ -2571,7 +2580,7 @@
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
@@ -2579,25 +2588,25 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
-      <c r="E151" s="4">
-        <v>18</v>
-      </c>
+      <c r="E151" s="4"/>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
+      <c r="E152" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
@@ -2605,7 +2614,7 @@
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -2613,29 +2622,29 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C155" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D155" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E155" s="14">
-        <v>16</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="C156" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D156" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E156" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2643,7 +2652,7 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -2651,7 +2660,7 @@
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
@@ -2659,7 +2668,7 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -2667,7 +2676,7 @@
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2675,29 +2684,29 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C162" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D162" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E162" s="14">
-        <v>18</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-      <c r="E163" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="C163" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D163" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E163" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
@@ -2705,7 +2714,7 @@
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
@@ -2713,115 +2722,131 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C166" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D166" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E166" s="13">
-        <v>42</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C167" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D167" s="22">
-        <v>44688</v>
-      </c>
-      <c r="E167" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="C167" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D167" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E167" s="13">
+        <v>42</v>
+      </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4">
-        <v>6</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C168" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D168" s="22">
+        <v>44688</v>
+      </c>
+      <c r="E168" s="4"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C169" s="21">
-        <v>45494</v>
-      </c>
-      <c r="D169" s="21">
-        <v>45494</v>
-      </c>
-      <c r="E169" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C170" s="33"/>
-      <c r="D170" s="33"/>
-      <c r="E170" s="4">
-        <v>20</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C170" s="35">
+        <v>45494</v>
+      </c>
+      <c r="D170" s="35">
+        <v>45494</v>
+      </c>
+      <c r="E170" s="4"/>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C171" s="4"/>
-      <c r="D171" s="4"/>
-      <c r="E171" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="C171" s="30"/>
+      <c r="D171" s="30"/>
+      <c r="E171" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C172" s="32">
-        <v>42350</v>
-      </c>
-      <c r="D172" s="34">
-        <v>42532</v>
-      </c>
-      <c r="E172" s="13">
-        <v>21</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C173" s="29">
-        <v>44436</v>
-      </c>
-      <c r="D173" s="30"/>
-      <c r="E173" s="4"/>
+        <v>161</v>
+      </c>
+      <c r="C173" s="32">
+        <v>42350</v>
+      </c>
+      <c r="D173" s="33">
+        <v>42532</v>
+      </c>
+      <c r="E173" s="13">
+        <v>21</v>
+      </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C174" s="29">
+        <v>44436</v>
+      </c>
+      <c r="D174" s="30"/>
+      <c r="E174" s="4"/>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B175" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C174" s="28"/>
-      <c r="D174" s="28"/>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B175" s="23" t="s">
+      <c r="C175" s="28"/>
+      <c r="D175" s="28"/>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B176" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C175" s="27">
+      <c r="C176" s="27">
         <v>45917</v>
       </c>
-      <c r="D175" s="27">
+      <c r="D176" s="27">
         <v>45917</v>
       </c>
     </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B177" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C177" s="24">
+        <v>46245</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E175">
-    <sortCondition ref="B3:B175"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E177">
+    <sortCondition ref="B3:B177"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F2D64B-E5FB-43EB-8F85-04E6B130F494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D03F5A-52CD-4481-AE2A-85234F58F5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,14 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>Nombre</t>
   </si>
   <si>
-    <t>Adolfo</t>
-  </si>
-  <si>
     <t>Adrián</t>
   </si>
   <si>
@@ -574,6 +571,21 @@
   </si>
   <si>
     <t>Zenobi, Thiago</t>
+  </si>
+  <si>
+    <t>Gonza, de Pacha</t>
+  </si>
+  <si>
+    <t>Fernández Rivas, Ignacio</t>
+  </si>
+  <si>
+    <t>Charpin, Juan Pablo</t>
+  </si>
+  <si>
+    <t>Cabas, Nicolás</t>
+  </si>
+  <si>
+    <t>Enz, Adolfo</t>
   </si>
 </sst>
 </file>
@@ -815,8 +827,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1099,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E177"/>
+  <dimension ref="B2:E181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -1114,18 +1126,18 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" t="s">
         <v>164</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>165</v>
-      </c>
-      <c r="E2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1153,7 +1165,9 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1161,9 +1175,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
@@ -1193,56 +1205,56 @@
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="C11" s="5">
+        <v>45472</v>
+      </c>
+      <c r="D11" s="5">
+        <v>45472</v>
+      </c>
+      <c r="E11" s="4">
+        <v>19</v>
+      </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>45472</v>
-      </c>
-      <c r="D12" s="5">
-        <v>45472</v>
-      </c>
-      <c r="E12" s="4">
-        <v>19</v>
-      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="C13" s="5">
+        <v>45361</v>
+      </c>
+      <c r="D13" s="5">
+        <v>45396</v>
+      </c>
+      <c r="E13" s="4">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>45361</v>
+        <v>45164</v>
       </c>
       <c r="D14" s="5">
-        <v>45396</v>
-      </c>
-      <c r="E14" s="4">
-        <v>9</v>
-      </c>
+        <v>45200</v>
+      </c>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="5">
-        <v>45164</v>
-      </c>
-      <c r="D15" s="5">
-        <v>45200</v>
-      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -1257,19 +1269,23 @@
       <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="C17" s="6">
+        <v>44422</v>
+      </c>
+      <c r="D17" s="6">
+        <v>44436</v>
+      </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="6">
-        <v>44422</v>
-      </c>
-      <c r="D18" s="6">
-        <v>44436</v>
+      <c r="C18" s="5">
+        <v>44793</v>
+      </c>
+      <c r="D18" s="5">
+        <v>44807</v>
       </c>
       <c r="E18" s="4"/>
     </row>
@@ -1277,11 +1293,11 @@
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="5">
-        <v>44793</v>
-      </c>
-      <c r="D19" s="5">
-        <v>44807</v>
+      <c r="C19" s="7">
+        <v>45220</v>
+      </c>
+      <c r="D19" s="7">
+        <v>45220</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -1289,12 +1305,8 @@
       <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="7">
-        <v>45220</v>
-      </c>
-      <c r="D20" s="7">
-        <v>45220</v>
-      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
@@ -1317,20 +1329,20 @@
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D23" s="8">
+        <v>45423</v>
+      </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="8">
-        <v>45346</v>
-      </c>
-      <c r="D24" s="8">
-        <v>45423</v>
-      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
@@ -1339,42 +1351,42 @@
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="4">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4">
-        <v>19</v>
+      <c r="C26" s="9">
+        <v>44739</v>
+      </c>
+      <c r="D26" s="9">
+        <v>44746</v>
+      </c>
+      <c r="E26" s="10">
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="9">
-        <v>44739</v>
-      </c>
-      <c r="D27" s="9">
-        <v>44746</v>
-      </c>
-      <c r="E27" s="10">
-        <v>44</v>
-      </c>
+      <c r="C27" s="8">
+        <v>45164</v>
+      </c>
+      <c r="D27" s="11">
+        <v>45220</v>
+      </c>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="8">
-        <v>45164</v>
-      </c>
-      <c r="D28" s="11">
-        <v>45220</v>
-      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
@@ -1386,16 +1398,19 @@
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="B30" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="24">
+        <v>46261</v>
+      </c>
+      <c r="D30" s="24">
+        <v>46261</v>
+      </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -1403,7 +1418,7 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="12">
@@ -1415,7 +1430,7 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -1423,7 +1438,7 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -1433,7 +1448,7 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="8">
         <v>44758</v>
@@ -1447,7 +1462,7 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1455,7 +1470,7 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1465,7 +1480,7 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -1473,23 +1488,26 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="B40" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" s="24">
+        <v>46261</v>
+      </c>
+      <c r="D40" s="24">
+        <v>46261</v>
+      </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -1497,7 +1515,7 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -1505,7 +1523,7 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -1513,7 +1531,7 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -1521,237 +1539,237 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="8">
-        <v>45395</v>
-      </c>
-      <c r="D45" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E45" s="14">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="C46" s="8">
+        <v>45395</v>
+      </c>
+      <c r="D46" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E46" s="14">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" s="12">
-        <v>43652</v>
-      </c>
-      <c r="D47" s="12">
-        <v>43722</v>
-      </c>
-      <c r="E47" s="13">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="C48" s="12">
+        <v>43652</v>
+      </c>
+      <c r="D48" s="12">
+        <v>43722</v>
+      </c>
+      <c r="E48" s="13">
+        <v>12</v>
+      </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="15">
-        <v>42294</v>
-      </c>
-      <c r="D49" s="12">
-        <v>42294</v>
-      </c>
-      <c r="E49" s="13">
-        <v>22</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="C50" s="15">
+        <v>42294</v>
+      </c>
+      <c r="D50" s="12">
+        <v>42294</v>
+      </c>
+      <c r="E50" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4">
-        <v>8</v>
-      </c>
+      <c r="E51" s="4"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="8">
-        <v>45395</v>
-      </c>
-      <c r="D52" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E52" s="14">
-        <v>9</v>
+        <v>47</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4">
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="12">
-        <v>42161</v>
-      </c>
-      <c r="E53" s="13">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="C53" s="8">
+        <v>45395</v>
+      </c>
+      <c r="D53" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E53" s="14">
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C54" s="9">
-        <v>44739</v>
-      </c>
-      <c r="D54" s="9">
-        <v>44746</v>
-      </c>
-      <c r="E54" s="10">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="12">
+        <v>42161</v>
+      </c>
+      <c r="E54" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" s="8">
-        <v>43708</v>
-      </c>
-      <c r="D55" s="8">
-        <v>44716</v>
-      </c>
-      <c r="E55" s="13">
-        <v>35</v>
+        <v>50</v>
+      </c>
+      <c r="C55" s="9">
+        <v>44739</v>
+      </c>
+      <c r="D55" s="9">
+        <v>44746</v>
+      </c>
+      <c r="E55" s="10">
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C56" s="8">
-        <v>44961</v>
+        <v>43708</v>
       </c>
       <c r="D56" s="8">
-        <v>45038</v>
+        <v>44716</v>
       </c>
       <c r="E56" s="13">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C57" s="8">
-        <v>45346</v>
+        <v>44961</v>
       </c>
       <c r="D57" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E57" s="14">
-        <v>24</v>
+        <v>45038</v>
+      </c>
+      <c r="E57" s="13">
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C58" s="8">
-        <v>45374</v>
+        <v>45346</v>
       </c>
       <c r="D58" s="8">
         <v>45423</v>
       </c>
-      <c r="E58" s="4"/>
+      <c r="E58" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="C59" s="8">
+        <v>45374</v>
+      </c>
+      <c r="D59" s="8">
+        <v>45423</v>
+      </c>
       <c r="E59" s="4"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="9">
-        <v>44226</v>
-      </c>
-      <c r="D60" s="9">
-        <v>44436</v>
-      </c>
-      <c r="E60" s="10">
-        <v>26</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="C61" s="9">
+        <v>44226</v>
+      </c>
+      <c r="D61" s="9">
+        <v>44436</v>
+      </c>
+      <c r="E61" s="10">
+        <v>26</v>
+      </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="12">
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="12">
         <v>42161</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E63" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B63" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="C63" s="24">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B64" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C64" s="24">
         <v>46060</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -1759,15 +1777,15 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
-        <v>63</v>
+      <c r="B67" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
@@ -1775,195 +1793,183 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C68" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D68" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E68" s="14">
-        <v>8</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B69" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C69" s="27">
-        <v>46183</v>
-      </c>
-      <c r="D69" s="27">
-        <v>46183</v>
-      </c>
+      <c r="B69" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="B70" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" s="24">
+        <v>46256</v>
+      </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="C71" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D71" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E71" s="14">
+        <v>8</v>
+      </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B72" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
+      <c r="B72" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C72" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D72" s="27">
+        <v>46183</v>
+      </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C73" s="12">
-        <v>43890</v>
-      </c>
-      <c r="D73" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E73" s="13">
-        <v>27</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C74" s="8">
-        <v>45361</v>
-      </c>
-      <c r="D74" s="8">
-        <v>45403</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
       <c r="E74" s="4"/>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C75" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D75" s="8">
-        <v>45417</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
       <c r="E75" s="4"/>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="C76" s="12">
+        <v>43890</v>
+      </c>
+      <c r="D76" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E76" s="13">
+        <v>27</v>
+      </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="C77" s="8">
+        <v>45361</v>
+      </c>
+      <c r="D77" s="8">
+        <v>45403</v>
+      </c>
       <c r="E77" s="4"/>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4">
-        <v>14</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C78" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D78" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E78" s="4"/>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B79" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C79" s="20">
-        <v>45913</v>
-      </c>
-      <c r="D79" s="20">
-        <v>45913</v>
-      </c>
+      <c r="B79" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
       <c r="E79" s="4"/>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B81" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C81" s="27">
-        <v>46183</v>
-      </c>
-      <c r="D81" s="27">
-        <v>46183</v>
+      <c r="B81" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4">
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B82" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
+      <c r="B82" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C82" s="20">
+        <v>45913</v>
+      </c>
+      <c r="D82" s="20">
+        <v>45913</v>
+      </c>
       <c r="E82" s="4"/>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B84" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C84" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D84" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E84" s="14">
-        <v>31</v>
+      <c r="B84" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="24">
+        <v>46252</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B85" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C85" s="12">
-        <v>41832</v>
-      </c>
-      <c r="D85" s="12">
-        <v>41832</v>
-      </c>
-      <c r="E85" s="13">
-        <v>23</v>
+      <c r="B85" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D85" s="27">
+        <v>46183</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -1971,7 +1977,7 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -1979,33 +1985,43 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="C88" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D88" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E88" s="14">
+        <v>31</v>
+      </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="C89" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D89" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E89" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="4">
-        <v>13</v>
-      </c>
+      <c r="E90" s="4"/>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -2013,37 +2029,33 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="4">
-        <v>22</v>
-      </c>
+      <c r="E92" s="4"/>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B94" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C94" s="21">
-        <v>45892</v>
-      </c>
-      <c r="D94" s="21">
-        <v>45892</v>
-      </c>
-      <c r="E94" s="4"/>
+      <c r="B94" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -2051,35 +2063,37 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" s="16">
-        <v>44723</v>
-      </c>
-      <c r="D96" s="16">
-        <v>44723</v>
-      </c>
-      <c r="E96" s="4"/>
+        <v>84</v>
+      </c>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B98" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
+      <c r="B98" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C98" s="21">
+        <v>45892</v>
+      </c>
+      <c r="D98" s="21">
+        <v>45892</v>
+      </c>
       <c r="E98" s="4"/>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -2087,15 +2101,19 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
+        <v>87</v>
+      </c>
+      <c r="C100" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D100" s="16">
+        <v>44723</v>
+      </c>
       <c r="E100" s="4"/>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -2103,7 +2121,7 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -2111,7 +2129,7 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -2119,7 +2137,7 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -2127,19 +2145,15 @@
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C105" s="21">
-        <v>45689</v>
-      </c>
-      <c r="D105" s="21">
-        <v>45773</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
       <c r="E105" s="4"/>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -2147,17 +2161,15 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
-      <c r="E107" s="4">
-        <v>4</v>
-      </c>
+      <c r="E107" s="4"/>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -2165,55 +2177,45 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="C109" s="21">
+        <v>45689</v>
+      </c>
+      <c r="D109" s="21">
+        <v>45773</v>
+      </c>
       <c r="E109" s="4"/>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C110" s="16">
-        <v>44961</v>
-      </c>
-      <c r="D110" s="16">
-        <v>45038</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
       <c r="E110" s="4"/>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C111" s="8">
-        <v>45403</v>
-      </c>
-      <c r="D111" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E111" s="14">
-        <v>29</v>
+        <v>98</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C112" s="8">
-        <v>45346</v>
-      </c>
-      <c r="D112" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E112" s="14">
-        <v>10</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -2221,37 +2223,47 @@
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C114" s="8">
+        <v>101</v>
+      </c>
+      <c r="C114" s="16">
         <v>44961</v>
       </c>
-      <c r="D114" s="8">
-        <v>45080</v>
-      </c>
-      <c r="E114" s="14">
-        <v>3</v>
-      </c>
+      <c r="D114" s="16">
+        <v>45038</v>
+      </c>
+      <c r="E114" s="4"/>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="C115" s="8">
+        <v>45403</v>
+      </c>
+      <c r="D115" s="8">
+        <v>45403</v>
+      </c>
+      <c r="E115" s="14">
+        <v>29</v>
+      </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="C116" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D116" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E116" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
@@ -2259,97 +2271,95 @@
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="C118" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D118" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E118" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B119" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C119" s="24">
-        <v>46238</v>
-      </c>
+      <c r="B119" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B121" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C121" s="21">
-        <v>45885</v>
-      </c>
-      <c r="D121" s="21">
-        <v>45885</v>
-      </c>
+      <c r="B121" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
       <c r="E121" s="4"/>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C122" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D122" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E122" s="14">
-        <v>24</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B123" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
+      <c r="B123" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C123" s="24">
+        <v>46238</v>
+      </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B125" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C125" s="8">
-        <v>45556</v>
-      </c>
-      <c r="D125" s="8">
-        <v>45556</v>
+      <c r="B125" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C125" s="21">
+        <v>45885</v>
+      </c>
+      <c r="D125" s="21">
+        <v>45885</v>
       </c>
       <c r="E125" s="4"/>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B126" s="19" t="s">
-        <v>116</v>
+      <c r="B126" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C126" s="8">
-        <v>45273</v>
+        <v>45417</v>
       </c>
       <c r="D126" s="8">
-        <v>45273</v>
-      </c>
-      <c r="E126" s="4"/>
+        <v>45417</v>
+      </c>
+      <c r="E126" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
@@ -2357,7 +2367,7 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
@@ -2365,23 +2375,31 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="C129" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D129" s="8">
+        <v>45556</v>
+      </c>
       <c r="E129" s="4"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
+      <c r="B130" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C130" s="8">
+        <v>45273</v>
+      </c>
+      <c r="D130" s="8">
+        <v>45273</v>
+      </c>
       <c r="E130" s="4"/>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -2389,21 +2407,15 @@
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C132" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D132" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E132" s="13">
-        <v>24</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
@@ -2411,7 +2423,7 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
@@ -2419,7 +2431,7 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
@@ -2427,120 +2439,111 @@
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C136" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D136" s="12">
+        <v>121</v>
+      </c>
+      <c r="C136" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D136" s="17">
         <v>44436</v>
       </c>
       <c r="E136" s="13">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B138" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="C138" s="24">
-        <v>45982</v>
-      </c>
+      <c r="B138" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C139" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D139" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E139" s="14">
-        <v>15</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4">
-        <v>11</v>
+        <v>125</v>
+      </c>
+      <c r="C140" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D140" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E140" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C141" s="15">
-        <v>39760</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C141" s="4"/>
       <c r="D141" s="4"/>
-      <c r="E141" s="4">
-        <v>3</v>
-      </c>
+      <c r="E141" s="4"/>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B142" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
+      <c r="B142" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C142" s="24">
+        <v>45982</v>
+      </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C143" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D143" s="12">
-        <v>45080</v>
+        <v>127</v>
+      </c>
+      <c r="C143" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D143" s="18">
+        <v>45220</v>
       </c>
       <c r="E143" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C144" s="8">
-        <v>44811</v>
-      </c>
-      <c r="D144" s="8">
-        <v>44811</v>
-      </c>
-      <c r="E144" s="13">
-        <v>41</v>
+        <v>128</v>
+      </c>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4">
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B145" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C145" s="24">
-        <v>45993</v>
-      </c>
-      <c r="D145" s="24">
-        <v>45993</v>
+      <c r="B145" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C145" s="15">
+        <v>39760</v>
+      </c>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
@@ -2548,39 +2551,46 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C147" s="12">
-        <v>44739</v>
+        <v>45003</v>
       </c>
       <c r="D147" s="12">
-        <v>44754</v>
-      </c>
-      <c r="E147" s="13">
-        <v>37</v>
+        <v>45080</v>
+      </c>
+      <c r="E147" s="14">
+        <v>14</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
+        <v>132</v>
+      </c>
+      <c r="C148" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D148" s="8">
+        <v>44811</v>
+      </c>
       <c r="E148" s="13">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B149" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
+      <c r="B149" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C149" s="24">
+        <v>45993</v>
+      </c>
+      <c r="D149" s="24">
+        <v>45993</v>
+      </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
@@ -2588,25 +2598,31 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
+        <v>134</v>
+      </c>
+      <c r="C151" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D151" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E151" s="13">
+        <v>37</v>
+      </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
-      <c r="E152" s="4">
-        <v>18</v>
+      <c r="E152" s="13">
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
@@ -2614,7 +2630,7 @@
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -2622,7 +2638,7 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -2630,21 +2646,17 @@
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C156" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D156" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E156" s="14">
-        <v>16</v>
+        <v>139</v>
+      </c>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4">
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2652,7 +2664,7 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -2660,7 +2672,7 @@
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
@@ -2668,15 +2680,21 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="C160" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D160" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E160" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2684,7 +2702,7 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
@@ -2692,21 +2710,15 @@
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C163" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D163" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E163" s="14">
-        <v>18</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
@@ -2714,7 +2726,7 @@
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
@@ -2722,7 +2734,7 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
@@ -2730,123 +2742,161 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C167" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D167" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E167" s="13">
-        <v>42</v>
+        <v>150</v>
+      </c>
+      <c r="C167" s="11">
+        <v>45423</v>
+      </c>
+      <c r="D167" s="11">
+        <v>45423</v>
+      </c>
+      <c r="E167" s="14">
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C168" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D168" s="22">
-        <v>44688</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
       <c r="E168" s="4"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
-      <c r="E169" s="4">
-        <v>6</v>
-      </c>
+      <c r="E169" s="4"/>
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="C170" s="35">
-        <v>45494</v>
-      </c>
-      <c r="D170" s="35">
-        <v>45494</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C170" s="35"/>
+      <c r="D170" s="35"/>
       <c r="E170" s="4"/>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C171" s="30"/>
-      <c r="D171" s="30"/>
-      <c r="E171" s="4">
-        <v>20</v>
+        <v>154</v>
+      </c>
+      <c r="C171" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D171" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E171" s="13">
+        <v>42</v>
       </c>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="C172" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D172" s="22">
+        <v>44688</v>
+      </c>
       <c r="E172" s="4"/>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C173" s="32">
-        <v>42350</v>
-      </c>
-      <c r="D173" s="33">
-        <v>42532</v>
-      </c>
-      <c r="E173" s="13">
-        <v>21</v>
+        <v>156</v>
+      </c>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4">
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C174" s="29">
-        <v>44436</v>
-      </c>
-      <c r="D174" s="30"/>
+        <v>157</v>
+      </c>
+      <c r="C174" s="27">
+        <v>45494</v>
+      </c>
+      <c r="D174" s="27">
+        <v>45494</v>
+      </c>
       <c r="E174" s="4"/>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="C175" s="28"/>
-      <c r="D175" s="28"/>
+        <v>158</v>
+      </c>
+      <c r="C175" s="30"/>
+      <c r="D175" s="30"/>
+      <c r="E175" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B176" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="C176" s="27">
+      <c r="B176" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B177" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C177" s="32">
+        <v>42350</v>
+      </c>
+      <c r="D177" s="33">
+        <v>42532</v>
+      </c>
+      <c r="E177" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B178" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="C178" s="29">
+        <v>44436</v>
+      </c>
+      <c r="D178" s="30"/>
+      <c r="E178" s="4"/>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B179" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C179" s="28"/>
+      <c r="D179" s="28"/>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B180" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C180" s="27">
         <v>45917</v>
       </c>
-      <c r="D176" s="27">
+      <c r="D180" s="27">
         <v>45917</v>
       </c>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B177" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="C177" s="24">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B181" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="C181" s="24">
         <v>46245</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E177">
-    <sortCondition ref="B3:B177"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E181">
+    <sortCondition ref="B3:B181"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D03F5A-52CD-4481-AE2A-85234F58F5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4A02BA-6A95-44EC-8711-AC8BA0FE648C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,9 +366,6 @@
     <t>Nicolás el messias</t>
   </si>
   <si>
-    <t>Nicolás, de Misio</t>
-  </si>
-  <si>
     <t>Nuñez, Juan Ignacio</t>
   </si>
   <si>
@@ -586,6 +583,9 @@
   </si>
   <si>
     <t>Enz, Adolfo</t>
+  </si>
+  <si>
+    <t>Torales, Nicolás</t>
   </si>
 </sst>
 </file>
@@ -1126,18 +1126,18 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" t="s">
         <v>163</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>164</v>
-      </c>
-      <c r="E2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C30" s="24">
         <v>46261</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C40" s="24">
         <v>46261</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C64" s="24">
         <v>46060</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C70" s="24">
         <v>46256</v>
@@ -1831,7 +1831,7 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C72" s="27">
         <v>46183</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C82" s="20">
         <v>45913</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C84" s="24">
         <v>46252</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C85" s="27">
         <v>46183</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C98" s="21">
         <v>45892</v>
@@ -2308,54 +2308,54 @@
       <c r="E121" s="4"/>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C122" s="24">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B123" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B123" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C123" s="24">
-        <v>46238</v>
-      </c>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C124" s="21">
+        <v>45885</v>
+      </c>
+      <c r="D124" s="21">
+        <v>45885</v>
+      </c>
+      <c r="E124" s="4"/>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B125" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B125" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C125" s="21">
-        <v>45885</v>
-      </c>
-      <c r="D125" s="21">
-        <v>45885</v>
-      </c>
-      <c r="E125" s="4"/>
+      <c r="C125" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D125" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E125" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C126" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D126" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E126" s="14">
-        <v>24</v>
-      </c>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
@@ -2369,32 +2369,32 @@
       <c r="B128" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
+      <c r="C128" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D128" s="8">
+        <v>45556</v>
+      </c>
       <c r="E128" s="4"/>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="19" t="s">
         <v>114</v>
       </c>
       <c r="C129" s="8">
-        <v>45556</v>
+        <v>45273</v>
       </c>
       <c r="D129" s="8">
-        <v>45556</v>
+        <v>45273</v>
       </c>
       <c r="E129" s="4"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="19" t="s">
+      <c r="B130" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C130" s="8">
-        <v>45273</v>
-      </c>
-      <c r="D130" s="8">
-        <v>45273</v>
-      </c>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
       <c r="E130" s="4"/>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
@@ -2433,23 +2433,23 @@
       <c r="B135" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="4"/>
+      <c r="C135" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D135" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E135" s="13">
+        <v>24</v>
+      </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C136" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D136" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E136" s="13">
-        <v>24</v>
-      </c>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
@@ -2471,143 +2471,145 @@
       <c r="B139" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
+      <c r="C139" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D139" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E139" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C140" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D140" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E140" s="13">
-        <v>1</v>
-      </c>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C141" s="24">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B142" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B142" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C142" s="24">
-        <v>45982</v>
+      <c r="C142" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D142" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E142" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C143" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D143" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E143" s="14">
-        <v>15</v>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4">
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C144" s="4"/>
+      <c r="C144" s="15">
+        <v>39760</v>
+      </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C145" s="15">
-        <v>39760</v>
-      </c>
+      <c r="C145" s="4"/>
       <c r="D145" s="4"/>
-      <c r="E145" s="4">
-        <v>3</v>
-      </c>
+      <c r="E145" s="4"/>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
+      <c r="C146" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D146" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E146" s="14">
+        <v>14</v>
+      </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C147" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D147" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E147" s="14">
-        <v>14</v>
+      <c r="C147" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D147" s="8">
+        <v>44811</v>
+      </c>
+      <c r="E147" s="13">
+        <v>41</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C148" s="24">
+        <v>45993</v>
+      </c>
+      <c r="D148" s="24">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B149" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C148" s="8">
-        <v>44811</v>
-      </c>
-      <c r="D148" s="8">
-        <v>44811</v>
-      </c>
-      <c r="E148" s="13">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B149" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="C149" s="24">
-        <v>45993</v>
-      </c>
-      <c r="D149" s="24">
-        <v>45993</v>
-      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
-      <c r="E150" s="4"/>
+      <c r="C150" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D150" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E150" s="13">
+        <v>37</v>
+      </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C151" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D151" s="12">
-        <v>44754</v>
-      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
       <c r="E151" s="13">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
@@ -2616,9 +2618,7 @@
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
-      <c r="E152" s="13">
-        <v>29</v>
-      </c>
+      <c r="E152" s="4"/>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
@@ -2642,7 +2642,9 @@
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
+      <c r="E155" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
@@ -2650,9 +2652,7 @@
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
-      <c r="E156" s="4">
-        <v>18</v>
-      </c>
+      <c r="E156" s="4"/>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
@@ -2674,23 +2674,23 @@
       <c r="B159" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
+      <c r="C159" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D159" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E159" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C160" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D160" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E160" s="14">
-        <v>16</v>
-      </c>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
@@ -2725,16 +2725,20 @@
       <c r="E164" s="4"/>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B165" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
+      <c r="B165" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C165" s="5">
+        <v>45585</v>
+      </c>
+      <c r="D165" s="5">
+        <v>45585</v>
+      </c>
       <c r="E165" s="4"/>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
@@ -2742,7 +2746,7 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C167" s="11">
         <v>45423</v>
@@ -2756,7 +2760,7 @@
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
@@ -2764,7 +2768,7 @@
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
@@ -2772,7 +2776,7 @@
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C170" s="35"/>
       <c r="D170" s="35"/>
@@ -2780,7 +2784,7 @@
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C171" s="17">
         <v>44660</v>
@@ -2794,7 +2798,7 @@
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C172" s="22">
         <v>44688</v>
@@ -2806,7 +2810,7 @@
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
@@ -2816,7 +2820,7 @@
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C174" s="27">
         <v>45494</v>
@@ -2828,7 +2832,7 @@
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C175" s="30"/>
       <c r="D175" s="30"/>
@@ -2838,7 +2842,7 @@
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B176" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
@@ -2846,7 +2850,7 @@
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C177" s="32">
         <v>42350</v>
@@ -2860,7 +2864,7 @@
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C178" s="29">
         <v>44436</v>
@@ -2870,14 +2874,14 @@
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C179" s="28"/>
       <c r="D179" s="28"/>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B180" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C180" s="27">
         <v>45917</v>
@@ -2888,7 +2892,7 @@
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B181" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C181" s="24">
         <v>46245</v>
@@ -2896,7 +2900,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E181">
-    <sortCondition ref="B3:B181"/>
+    <sortCondition ref="B2:B181"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
